--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q40_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006648406437933363</v>
+        <v>0.0002775149266206472</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006648406437933363</v>
+        <v>0.0002775149266206472</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006575082174812866</v>
+        <v>0.000274254707234564</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006575082174812866</v>
+        <v>0.000274254707234564</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0007570657568489346</v>
+        <v>0.0003191469005746673</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007570657568489346</v>
+        <v>0.0003191469005746673</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001047294915230456</v>
+        <v>0.0004465483253021145</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001047294915230456</v>
+        <v>0.0004465483253021145</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001500605967093579</v>
+        <v>0.0006417999829682255</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001500605967093579</v>
+        <v>0.0006417999829682255</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001992803767356363</v>
+        <v>0.0008492815783034413</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001992803767356363</v>
+        <v>0.0008492815783034413</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002559077607555967</v>
+        <v>0.001088024683740848</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002559077607555967</v>
+        <v>0.001088024683740848</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003199395452122018</v>
+        <v>0.001361471721638224</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003199395452122018</v>
+        <v>0.001361471721638224</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003753370752844778</v>
+        <v>0.001599712059755459</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003753370752844778</v>
+        <v>0.001599712059755459</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004134893448437589</v>
+        <v>0.001763270347096297</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004134893448437589</v>
+        <v>0.001763270347096297</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004317179061605954</v>
+        <v>0.001840553460581454</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004317179061605954</v>
+        <v>0.001840553460581454</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00437523698318963</v>
+        <v>0.00186425708183901</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00437523698318963</v>
+        <v>0.00186425708183901</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.004304534037945073</v>
+        <v>0.001833502597353314</v>
       </c>
       <c r="C14" t="n">
-        <v>0.004304534037945073</v>
+        <v>0.001833502597353314</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.004191330730419067</v>
+        <v>0.001785338125876202</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004191330730419067</v>
+        <v>0.001785338125876202</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003992225667656104</v>
+        <v>0.001700466105381716</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003992225667656104</v>
+        <v>0.001700466105381716</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003889112503116441</v>
+        <v>0.001656144889069458</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003889112503116441</v>
+        <v>0.001656144889069458</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003712924175885366</v>
+        <v>0.001583050711292306</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003712924175885366</v>
+        <v>0.001583050711292306</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003596861317074179</v>
+        <v>0.001533181533560791</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003596861317074179</v>
+        <v>0.001533181533560791</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003503818455666946</v>
+        <v>0.001495094878673683</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003503818455666946</v>
+        <v>0.001495094878673683</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.003417040719565562</v>
+        <v>0.001457836731296281</v>
       </c>
       <c r="C21" t="n">
-        <v>0.003417040719565562</v>
+        <v>0.001457836731296281</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
